--- a/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,64; 43,1</t>
+          <t>18,08; 43,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 23,02</t>
+          <t>-1,49; 22,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 14,95</t>
+          <t>-13,16; 14,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 23,97</t>
+          <t>-3,19; 22,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 24,38</t>
+          <t>5,7; 24,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 19,66</t>
+          <t>-0,04; 20,3</t>
         </is>
       </c>
     </row>
@@ -705,39 +705,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,74; 377,66</t>
+          <t>75,48; 404,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 191,17</t>
+          <t>-7,74; 192,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 60,79</t>
+          <t>-35,5; 57,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 101,44</t>
+          <t>-8,31; 94,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 123,69</t>
+          <t>18,24; 122,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 94,83</t>
+          <t>-0,98; 100,47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,82; 28,44</t>
+          <t>9,75; 28,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; -12,68</t>
+          <t>-26,24; -12,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 23,36</t>
+          <t>4,39; 24,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -16,16</t>
+          <t>-29,95; -16,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,64; 23,12</t>
+          <t>8,56; 23,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,17; -16,12</t>
+          <t>-25,07; -15,37</t>
         </is>
       </c>
     </row>
@@ -861,39 +861,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,45; 180,1</t>
+          <t>35,08; 192,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -76,64</t>
+          <t>-100,0; -75,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,59; 121,98</t>
+          <t>14,27; 122,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-98,31; -82,65</t>
+          <t>-98,59; -82,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,09; 123,51</t>
+          <t>32,54; 128,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-97,84; -85,16</t>
+          <t>-97,68; -84,94</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,61; 6,58</t>
+          <t>-15,67; 7,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 9,18</t>
+          <t>-12,75; 9,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,02; 9,01</t>
+          <t>-13,43; 6,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 8,96</t>
+          <t>-14,73; 7,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 4,05</t>
+          <t>-11,67; 4,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 5,35</t>
+          <t>-10,49; 5,09</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 39,55</t>
+          <t>-57,37; 41,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 58,81</t>
+          <t>-48,73; 65,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 69,75</t>
+          <t>-51,8; 52,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,85; 70,24</t>
+          <t>-56,44; 51,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,93; 23,84</t>
+          <t>-47,05; 24,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-43,77; 30,42</t>
+          <t>-41,91; 29,86</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 11,19</t>
+          <t>-12,42; 11,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 30,58</t>
+          <t>2,22; 30,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 1,93</t>
+          <t>-21,38; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,43; 45,22</t>
+          <t>4,77; 42,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 4,08</t>
+          <t>-14,04; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,12; 30,89</t>
+          <t>9,02; 32,63</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 45,61</t>
+          <t>-34,17; 48,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 116,78</t>
+          <t>5,47; 116,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,89; 8,39</t>
+          <t>-51,93; 9,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,4; 149,07</t>
+          <t>13,07; 140,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,49; 15,39</t>
+          <t>-36,79; 11,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,73; 101,24</t>
+          <t>23,83; 108,28</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,87; -0,32</t>
+          <t>-26,99; 0,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-33,98; -11,04</t>
+          <t>-32,9; -10,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-26,82; -0,47</t>
+          <t>-28,14; -2,45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,89; -15,21</t>
+          <t>-35,53; -14,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,46; -4,76</t>
+          <t>-22,89; -5,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,17; -15,51</t>
+          <t>-30,43; -15,36</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,2; 7,96</t>
+          <t>-86,65; 21,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,79</t>
+          <t>-100,0; -56,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 7,0</t>
+          <t>-83,24; -1,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1349,19 +1349,19 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-78,08; -20,51</t>
+          <t>-80,08; -23,65</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -80,41</t>
+          <t>-100,0; -79,6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 25,33</t>
+          <t>-4,14; 23,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -6,93</t>
+          <t>-30,42; -6,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 26,04</t>
+          <t>-3,27; 24,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 16,01</t>
+          <t>-11,27; 14,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 20,1</t>
+          <t>1,39; 20,47</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 1,69</t>
+          <t>-16,45; 2,1</t>
         </is>
       </c>
     </row>
@@ -1485,39 +1485,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 136,29</t>
+          <t>-12,92; 123,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-90,0; -31,08</t>
+          <t>-89,34; -24,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 166,47</t>
+          <t>-15,99; 173,05</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-46,84; 108,15</t>
+          <t>-45,93; 117,78</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2,07; 112,74</t>
+          <t>4,67; 115,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 13,0</t>
+          <t>-58,82; 13,43</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 14,58</t>
+          <t>-2,67; 14,47</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 13,01</t>
+          <t>-5,18; 13,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 14,25</t>
+          <t>-1,85; 15,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 17,19</t>
+          <t>-0,71; 18,06</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 11,88</t>
+          <t>-0,01; 12,22</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 13,62</t>
+          <t>-1,42; 12,75</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 85,76</t>
+          <t>-11,58; 88,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,59; 78,39</t>
+          <t>-20,89; 79,11</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 78,61</t>
+          <t>-7,45; 80,58</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 94,47</t>
+          <t>-3,71; 99,65</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 63,35</t>
+          <t>0,05; 64,99</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 69,28</t>
+          <t>-5,32; 67,28</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -2,06</t>
+          <t>-19,38; -2,29</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-48,77; -34,71</t>
+          <t>-48,58; -33,81</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-30,48; -13,48</t>
+          <t>-29,73; -12,31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -43,28</t>
+          <t>-57,02; -43,58</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,48; -10,25</t>
+          <t>-22,3; -10,4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-50,43; -40,95</t>
+          <t>-50,95; -41,48</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1797,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-37,51; -3,74</t>
+          <t>-38,52; -5,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-95,93; -82,9</t>
+          <t>-96,13; -83,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-53,61; -27,56</t>
+          <t>-51,48; -24,23</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-96,35; -85,97</t>
+          <t>-96,67; -86,54</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,43; -21,9</t>
+          <t>-41,69; -22,06</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,3; -87,68</t>
+          <t>-95,41; -88,09</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 7,48</t>
+          <t>-0,24; 7,45</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-15,98; -8,25</t>
+          <t>-16,09; -8,42</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 1,21</t>
+          <t>-6,91; 0,73</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -6,18</t>
+          <t>-15,14; -6,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 2,76</t>
+          <t>-2,72; 3,0</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -8,41</t>
+          <t>-14,37; -8,38</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 28,47</t>
+          <t>-0,83; 28,96</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-53,7; -31,48</t>
+          <t>-54,03; -31,62</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,87; 4,44</t>
+          <t>-20,7; 2,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-45,99; -20,81</t>
+          <t>-45,05; -19,29</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 9,69</t>
+          <t>-8,36; 10,43</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-46,38; -28,57</t>
+          <t>-46,02; -28,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 43,89</t>
+          <t>16,36; 42,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 22,3</t>
+          <t>-1,94; 22,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 14,42</t>
+          <t>-12,09; 15,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 22,84</t>
+          <t>-3,91; 24,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,7; 24,59</t>
+          <t>5,14; 24,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 20,3</t>
+          <t>1,27; 20,36</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,48; 404,08</t>
+          <t>72,44; 385,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 192,58</t>
+          <t>-10,16; 188,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 57,17</t>
+          <t>-32,1; 63,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 94,9</t>
+          <t>-10,32; 99,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,24; 122,42</t>
+          <t>16,3; 122,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 100,47</t>
+          <t>4,08; 104,79</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,75; 28,98</t>
+          <t>8,6; 28,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,24; -12,35</t>
+          <t>-26,03; -12,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 24,13</t>
+          <t>5,02; 24,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,95; -16,33</t>
+          <t>-29,82; -16,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,56; 23,73</t>
+          <t>9,45; 23,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,07; -15,37</t>
+          <t>-25,89; -16,44</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,08; 192,06</t>
+          <t>32,83; 187,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -75,11</t>
+          <t>-100,0; -74,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,27; 122,44</t>
+          <t>15,77; 130,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-98,59; -82,41</t>
+          <t>-98,57; -83,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,54; 128,5</t>
+          <t>37,69; 127,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-97,68; -84,94</t>
+          <t>-97,5; -85,61</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 7,01</t>
+          <t>-16,24; 7,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 9,49</t>
+          <t>-12,65; 9,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 6,95</t>
+          <t>-13,37; 8,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 7,43</t>
+          <t>-14,0; 6,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,28</t>
+          <t>-11,71; 3,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 5,09</t>
+          <t>-10,34; 4,89</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-57,37; 41,26</t>
+          <t>-58,68; 46,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-48,73; 65,04</t>
+          <t>-46,55; 56,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 52,78</t>
+          <t>-54,71; 62,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-56,44; 51,89</t>
+          <t>-54,22; 48,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 24,73</t>
+          <t>-46,21; 22,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,91; 29,86</t>
+          <t>-41,75; 29,16</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 11,86</t>
+          <t>-13,46; 10,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 30,04</t>
+          <t>0,67; 29,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,38; 2,74</t>
+          <t>-20,29; 3,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,77; 42,43</t>
+          <t>5,4; 42,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 3,62</t>
+          <t>-14,28; 3,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,02; 32,63</t>
+          <t>8,26; 32,68</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 48,54</t>
+          <t>-36,24; 41,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 116,28</t>
+          <t>1,65; 118,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,93; 9,19</t>
+          <t>-48,45; 16,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,07; 140,33</t>
+          <t>11,98; 139,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 11,3</t>
+          <t>-36,87; 10,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,83; 108,28</t>
+          <t>20,45; 110,16</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 0,06</t>
+          <t>-27,21; -0,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -10,62</t>
+          <t>-34,83; -11,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-28,14; -2,45</t>
+          <t>-27,32; -1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,53; -14,33</t>
+          <t>-35,61; -14,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -5,17</t>
+          <t>-22,15; -3,08</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-30,43; -15,36</t>
+          <t>-31,08; -16,04</t>
         </is>
       </c>
     </row>
@@ -1329,17 +1329,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-86,65; 21,69</t>
+          <t>-88,77; 8,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,54</t>
+          <t>-100,0; -37,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,24; -1,27</t>
+          <t>-83,07; -0,53</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-80,08; -23,65</t>
+          <t>-79,31; -14,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -79,6</t>
+          <t>-100,0; -83,33</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 23,83</t>
+          <t>-4,94; 23,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,42; -6,59</t>
+          <t>-30,34; -6,27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 24,06</t>
+          <t>-2,41; 25,43</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,27; 14,75</t>
+          <t>-10,03; 16,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,39; 20,47</t>
+          <t>0,75; 19,96</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 2,1</t>
+          <t>-16,78; 1,9</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 123,93</t>
+          <t>-15,99; 120,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,34; -24,94</t>
+          <t>-88,53; -24,36</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 173,05</t>
+          <t>-10,01; 191,06</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 117,78</t>
+          <t>-41,23; 117,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>4,67; 115,36</t>
+          <t>0,34; 109,3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 13,43</t>
+          <t>-59,04; 12,75</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 14,47</t>
+          <t>-3,11; 13,73</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 13,32</t>
+          <t>-5,04; 13,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 15,41</t>
+          <t>-2,88; 14,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 18,06</t>
+          <t>-1,11; 19,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 12,22</t>
+          <t>-0,31; 12,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 12,75</t>
+          <t>-0,25; 12,77</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 88,54</t>
+          <t>-13,23; 80,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-20,89; 79,11</t>
+          <t>-21,43; 82,28</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 80,58</t>
+          <t>-10,39; 80,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 99,65</t>
+          <t>-6,6; 100,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,05; 64,99</t>
+          <t>-1,11; 65,52</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 67,28</t>
+          <t>-0,52; 68,31</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -2,29</t>
+          <t>-19,0; -1,57</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-48,58; -33,81</t>
+          <t>-48,52; -35,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,73; -12,31</t>
+          <t>-29,78; -12,47</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-57,02; -43,58</t>
+          <t>-56,64; -43,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-22,3; -10,4</t>
+          <t>-21,98; -9,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-50,95; -41,48</t>
+          <t>-51,19; -40,86</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1797,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-38,52; -5,49</t>
+          <t>-38,26; -3,68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-96,13; -83,81</t>
+          <t>-95,57; -82,7</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-51,48; -24,23</t>
+          <t>-52,04; -25,85</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-96,67; -86,54</t>
+          <t>-96,69; -86,4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,69; -22,06</t>
+          <t>-41,01; -19,89</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,41; -88,09</t>
+          <t>-95,35; -87,6</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 7,45</t>
+          <t>-0,14; 7,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -8,42</t>
+          <t>-15,94; -8,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,73</t>
+          <t>-6,62; 1,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -6,16</t>
+          <t>-15,12; -5,85</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 3,0</t>
+          <t>-2,53; 2,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -8,38</t>
+          <t>-14,51; -8,19</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 28,96</t>
+          <t>-0,58; 28,14</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-54,03; -31,62</t>
+          <t>-53,43; -30,32</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 2,62</t>
+          <t>-19,59; 3,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-45,05; -19,29</t>
+          <t>-45,81; -18,96</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 10,43</t>
+          <t>-8,09; 9,33</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-46,02; -28,45</t>
+          <t>-46,63; -28,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$individual-Provincia-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción individual en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12,59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>30,61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,52</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>16,33</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>14,31</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16,36; 42,01</t>
+          <t>-12,31; 14,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 22,55</t>
+          <t>-0,91; 26,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 15,5</t>
+          <t>16,64; 43,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 24,12</t>
+          <t>4,04; 28,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,14; 24,57</t>
+          <t>4,75; 24,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,27; 20,36</t>
+          <t>4,18; 23,39</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40,07%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>178,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>61,16%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,44; 385,5</t>
+          <t>-34,16; 60,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 188,29</t>
+          <t>-2,64; 111,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 63,5</t>
+          <t>66,74; 377,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 99,17</t>
+          <t>16,49; 249,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 122,41</t>
+          <t>15,86; 123,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,08; 104,79</t>
+          <t>13,79; 114,1</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,96</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-22,78</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>19,27</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-18,72</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>13,96</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-22,51</t>
+          <t>-18,3</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,67</t>
+          <t>-20,61</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 28,94</t>
+          <t>3,3; 23,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; -12,6</t>
+          <t>-30,74; -16,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 24,2</t>
+          <t>8,82; 28,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,82; -16,18</t>
+          <t>-25,99; -12,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,45; 23,66</t>
+          <t>9,64; 23,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,89; -16,44</t>
+          <t>-26,02; -16,23</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58,18%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-94,94%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>96,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-93,5%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>58,18%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-93,8%</t>
+          <t>-91,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-93,68%</t>
+          <t>-93,42%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,83; 187,29</t>
+          <t>10,59; 121,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -74,69</t>
+          <t>-98,68; -86,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,77; 130,15</t>
+          <t>30,45; 180,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-98,57; -83,8</t>
+          <t>-100,0; -72,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,69; 127,52</t>
+          <t>38,09; 123,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-97,5; -85,61</t>
+          <t>-97,76; -84,36</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,77</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-4,41</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,76</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,28</t>
+          <t>-2,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,8</t>
+          <t>-2,57</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,24; 7,66</t>
+          <t>-13,02; 9,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 9,84</t>
+          <t>-12,98; 9,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 8,17</t>
+          <t>-18,61; 6,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 6,83</t>
+          <t>-14,85; 9,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,71; 3,64</t>
+          <t>-11,19; 4,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 4,89</t>
+          <t>-10,74; 5,38</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-13,85%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-13,88%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-19,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-9,5%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-13,85%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-16,44%</t>
+          <t>-10,6%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,26%</t>
+          <t>-12,2%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 46,33</t>
+          <t>-50,44; 69,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-46,55; 56,74</t>
+          <t>-51,63; 82,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,71; 62,86</t>
+          <t>-62,3; 39,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-54,22; 48,16</t>
+          <t>-50,74; 56,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,21; 22,1</t>
+          <t>-46,93; 23,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 29,16</t>
+          <t>-43,64; 30,16</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-9,64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22,24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,95</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15,75</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-9,64</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,62</t>
+          <t>17,41</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,46</t>
+          <t>19,84</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,46; 10,06</t>
+          <t>-21,06; 1,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 29,5</t>
+          <t>6,47; 43,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 3,84</t>
+          <t>-13,08; 11,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 42,05</t>
+          <t>2,87; 32,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 3,13</t>
+          <t>-14,63; 4,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,26; 32,68</t>
+          <t>6,83; 30,85</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-26,93%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-2,98%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>49,55%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-26,93%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-36,24; 41,02</t>
+          <t>-51,89; 8,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 118,38</t>
+          <t>13,68; 143,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,45; 16,32</t>
+          <t>-35,32; 45,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,98; 139,5</t>
+          <t>6,93; 123,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-36,87; 10,53</t>
+          <t>-37,49; 15,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,45; 110,16</t>
+          <t>17,43; 102,07</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-13,77</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-24,3</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-13,64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-21,28</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-13,77</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-24,3</t>
+          <t>-21,33</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-27,21; -0,51</t>
+          <t>-26,82; -0,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-34,83; -11,09</t>
+          <t>-35,89; -15,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-27,32; -1,67</t>
+          <t>-26,87; -0,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-35,61; -14,51</t>
+          <t>-33,94; -11,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -3,08</t>
+          <t>-22,46; -4,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-31,08; -16,04</t>
+          <t>-31,17; -15,49</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-56,68%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-59,64%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-92,99%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-56,68%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>-93,22%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-96,88%</t>
+          <t>-96,89%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,77; 8,72</t>
+          <t>-81,85; 7,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-83,07; -0,53</t>
+          <t>-88,2; 7,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -39,29</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-79,31; -14,83</t>
+          <t>-78,08; -20,51</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -83,33</t>
+          <t>-100,0; -80,55</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>11,25</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1,61</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>10,11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-17,85</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>11,25</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>-17,81</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,23</t>
+          <t>-7,74</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 23,95</t>
+          <t>-1,81; 26,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -6,27</t>
+          <t>-11,72; 15,94</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 25,43</t>
+          <t>-3,8; 25,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 16,04</t>
+          <t>-30,9; -7,07</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,75; 19,96</t>
+          <t>0,63; 20,1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 1,9</t>
+          <t>-16,34; 0,98</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>57,13%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8,15%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>37,96%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-67,01%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>57,13%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>-66,87%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-31,42%</t>
+          <t>-33,65%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 120,61</t>
+          <t>-12,22; 166,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-88,53; -24,36</t>
+          <t>-47,27; 105,58</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 191,06</t>
+          <t>-12,12; 136,29</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-41,23; 117,1</t>
+          <t>-89,52; -30,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,34; 109,3</t>
+          <t>2,07; 112,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 12,75</t>
+          <t>-60,48; 8,14</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>5,56</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10,57</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>3,65</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7,72</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>7,5</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 13,73</t>
+          <t>-2,27; 14,25</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 13,46</t>
+          <t>0,25; 20,02</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 14,19</t>
+          <t>-2,12; 14,58</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 19,0</t>
+          <t>-4,84; 13,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 12,2</t>
+          <t>-0,41; 11,88</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 12,77</t>
+          <t>1,47; 14,83</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>25,05%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>28,86%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,23; 80,87</t>
+          <t>-9,24; 78,61</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 82,28</t>
+          <t>0,89; 107,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 80,94</t>
+          <t>-8,99; 85,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 100,2</t>
+          <t>-19,51; 79,42</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 65,52</t>
+          <t>-1,89; 63,35</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 68,31</t>
+          <t>4,62; 77,74</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-21,81</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-50,11</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-10,58</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>-41,9</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-21,81</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>-49,89</t>
+          <t>-42,21</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1708,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-45,99</t>
+          <t>-46,25</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -1,57</t>
+          <t>-30,48; -13,48</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-48,52; -35,31</t>
+          <t>-56,78; -43,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-29,78; -12,47</t>
+          <t>-18,86; -2,06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-56,64; -43,02</t>
+          <t>-49,05; -35,13</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -9,34</t>
+          <t>-22,48; -10,25</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-51,19; -40,86</t>
+          <t>-50,7; -41,26</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-40,59%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-93,24%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>-23,03%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>-91,23%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-40,59%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-92,83%</t>
+          <t>-91,92%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1784,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-92,12%</t>
+          <t>-92,65%</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-38,26; -3,68</t>
+          <t>-53,61; -27,56</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-95,57; -82,7</t>
+          <t>-96,47; -86,04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,04; -25,85</t>
+          <t>-37,51; -3,74</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-96,69; -86,4</t>
+          <t>-96,27; -83,68</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-41,01; -19,89</t>
+          <t>-42,43; -21,9</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-95,35; -87,6</t>
+          <t>-95,61; -88,4</t>
         </is>
       </c>
     </row>
@@ -1839,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-11,06</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>3,59</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-12,07</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-2,99</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-11,08</t>
+          <t>-11,22</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1864,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-11,48</t>
+          <t>-11,1</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,37</t>
+          <t>-6,67; 1,21</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-15,94; -8,09</t>
+          <t>-15,22; -6,48</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 1,11</t>
+          <t>-0,71; 7,48</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -5,85</t>
+          <t>-14,84; -7,38</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,63</t>
+          <t>-2,75; 2,76</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -8,19</t>
+          <t>-14,19; -8,1</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-9,45%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-34,95%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>12,71%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-42,77%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-9,45%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-35,03%</t>
+          <t>-39,77%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-38,29%</t>
+          <t>-37,01%</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 28,14</t>
+          <t>-19,87; 4,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-53,43; -30,32</t>
+          <t>-46,0; -21,57</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 3,8</t>
+          <t>-2,4; 28,47</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-45,81; -18,96</t>
+          <t>-49,41; -28,26</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 9,33</t>
+          <t>-8,71; 9,69</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-46,63; -28,51</t>
+          <t>-44,93; -27,99</t>
         </is>
       </c>
     </row>
